--- a/Employee_Reports_wi52/Nove Manuel Menorisa Tagpuno Q0234.xlsx
+++ b/Employee_Reports_wi52/Nove Manuel Menorisa Tagpuno Q0234.xlsx
@@ -569,11 +569,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -618,11 +618,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -667,11 +667,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -716,11 +716,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -753,11 +753,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>723</v>
+        <v>715</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -790,11 +790,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>723</v>
+        <v>715</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -827,11 +827,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>723</v>
+        <v>715</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -864,11 +864,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>723</v>
+        <v>715</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -913,11 +913,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -962,11 +962,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1011,11 +1011,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1060,11 +1060,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1109,11 +1109,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1158,11 +1158,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1207,11 +1207,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>692</v>
+        <v>684</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1256,11 +1256,11 @@
         </is>
       </c>
       <c r="H18" s="3" t="n">
-        <v>692</v>
+        <v>684</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1305,11 +1305,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1354,11 +1354,11 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1403,11 +1403,11 @@
         </is>
       </c>
       <c r="H21" s="3" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -1452,11 +1452,11 @@
         </is>
       </c>
       <c r="H22" s="3" t="n">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -1501,11 +1501,11 @@
         </is>
       </c>
       <c r="H23" s="3" t="n">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -1550,11 +1550,11 @@
         </is>
       </c>
       <c r="H24" s="3" t="n">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -1599,11 +1599,11 @@
         </is>
       </c>
       <c r="H25" s="3" t="n">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -1636,11 +1636,11 @@
         </is>
       </c>
       <c r="H26" s="3" t="n">
-        <v>550</v>
+        <v>542</v>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -1685,11 +1685,11 @@
         </is>
       </c>
       <c r="H27" s="3" t="n">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -1735,11 +1735,11 @@
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-119</v>
+        <v>-127</v>
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
@@ -1784,11 +1784,11 @@
         </is>
       </c>
       <c r="H29" s="3" t="n">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
@@ -1833,11 +1833,11 @@
         </is>
       </c>
       <c r="H30" s="3" t="n">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
@@ -1870,11 +1870,11 @@
         </is>
       </c>
       <c r="H31" s="3" t="n">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
@@ -1919,11 +1919,11 @@
         </is>
       </c>
       <c r="H32" s="3" t="n">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
@@ -1968,11 +1968,11 @@
         </is>
       </c>
       <c r="H33" s="3" t="n">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
@@ -2017,11 +2017,11 @@
         </is>
       </c>
       <c r="H34" s="3" t="n">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
@@ -2066,11 +2066,11 @@
         </is>
       </c>
       <c r="H35" s="3" t="n">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
@@ -2115,11 +2115,11 @@
         </is>
       </c>
       <c r="H36" s="3" t="n">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
@@ -2164,11 +2164,11 @@
         </is>
       </c>
       <c r="H37" s="4" t="n">
-        <v>-22</v>
+        <v>-30</v>
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
@@ -2213,11 +2213,11 @@
         </is>
       </c>
       <c r="H38" s="4" t="n">
-        <v>-21</v>
+        <v>-29</v>
       </c>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J38" s="4" t="inlineStr">
@@ -2262,11 +2262,11 @@
         </is>
       </c>
       <c r="H39" s="4" t="n">
-        <v>-19</v>
+        <v>-27</v>
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J39" s="4" t="inlineStr">
@@ -2299,11 +2299,11 @@
         </is>
       </c>
       <c r="H40" s="4" t="n">
-        <v>-23</v>
+        <v>-31</v>
       </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J40" s="4" t="inlineStr">
@@ -2348,11 +2348,11 @@
         </is>
       </c>
       <c r="H41" s="4" t="n">
-        <v>-2</v>
+        <v>-10</v>
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J41" s="4" t="inlineStr">
@@ -2397,11 +2397,11 @@
         </is>
       </c>
       <c r="H42" s="4" t="n">
-        <v>-1</v>
+        <v>-9</v>
       </c>
       <c r="I42" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J42" s="4" t="inlineStr">
@@ -2434,11 +2434,11 @@
         </is>
       </c>
       <c r="H43" s="3" t="n">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
@@ -2483,11 +2483,11 @@
         </is>
       </c>
       <c r="H44" s="3" t="n">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
@@ -2520,11 +2520,11 @@
         </is>
       </c>
       <c r="H45" s="3" t="n">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
@@ -2569,11 +2569,11 @@
         </is>
       </c>
       <c r="H46" s="3" t="n">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
@@ -2606,11 +2606,11 @@
         </is>
       </c>
       <c r="H47" s="3" t="n">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="I47" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J47" s="3" t="inlineStr">
@@ -3245,7 +3245,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7527</v>
+        <v>7519</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7961</v>
+        <v>7953</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -3303,7 +3303,7 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>7961</v>
+        <v>7953</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7961</v>
+        <v>7953</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -3361,7 +3361,7 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>7961</v>
+        <v>7953</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -3390,7 +3390,7 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>7961</v>
+        <v>7953</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>7961</v>
+        <v>7953</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7955</v>
+        <v>7947</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -3543,7 +3543,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7956</v>
+        <v>7948</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -3572,7 +3572,7 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>7955</v>
+        <v>7947</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -3601,7 +3601,7 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7953</v>
+        <v>7945</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -3630,7 +3630,7 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>7953</v>
+        <v>7945</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -3659,7 +3659,7 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>7954</v>
+        <v>7946</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>7953</v>
+        <v>7945</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -3717,7 +3717,7 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>7953</v>
+        <v>7945</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -3746,7 +3746,7 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>7954</v>
+        <v>7946</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>7954</v>
+        <v>7946</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>7955</v>
+        <v>7947</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -3833,7 +3833,7 @@
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>7954</v>
+        <v>7946</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -3862,7 +3862,7 @@
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>7955</v>
+        <v>7947</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -3891,7 +3891,7 @@
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>7955</v>
+        <v>7947</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
@@ -3920,7 +3920,7 @@
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>7952</v>
+        <v>7944</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>7953</v>
+        <v>7945</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>7953</v>
+        <v>7945</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>7956</v>
+        <v>7948</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>7956</v>
+        <v>7948</v>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
@@ -4065,7 +4065,7 @@
         </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v>7952</v>
+        <v>7944</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>7953</v>
+        <v>7945</v>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
